--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486688_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486688_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8853</v>
+        <v>1.4896</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2761</v>
+        <v>-0.5725</v>
       </c>
       <c r="F2" t="n">
-        <v>2.1614</v>
+        <v>2.0621</v>
       </c>
       <c r="G2" t="n">
         <v>-2.0981</v>
@@ -610,13 +610,13 @@
         <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2923</v>
+        <v>-0.1034</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1663</v>
+        <v>-0.4626</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4585</v>
+        <v>0.3592</v>
       </c>
       <c r="V2" t="n">
         <v>3.1118</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3081</v>
+        <v>0.7232</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0344</v>
+        <v>1.3999</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.6766</v>
       </c>
       <c r="G3" t="n">
         <v>1.0543</v>
@@ -688,13 +688,13 @@
         <v>0.5792</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7116</v>
+        <v>-0.2964</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.745</v>
+        <v>-0.3796</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0335</v>
+        <v>0.08309999999999999</v>
       </c>
       <c r="V3" t="n">
         <v>-0.6138</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.5061</v>
+        <v>-1.2537</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.6272</v>
+        <v>-2.5237</v>
       </c>
       <c r="F4" t="n">
-        <v>1.121</v>
+        <v>1.27</v>
       </c>
       <c r="G4" t="n">
         <v>-1.131</v>
@@ -766,13 +766,13 @@
         <v>0.5792</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6455</v>
+        <v>-0.393</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3863</v>
+        <v>-0.2829</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2592</v>
+        <v>-0.1102</v>
       </c>
       <c r="V4" t="n">
         <v>0.6565</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.601</v>
+        <v>-1.7571</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4732</v>
+        <v>-1.1077</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1278</v>
+        <v>-0.6493</v>
       </c>
       <c r="G5" t="n">
         <v>-0.8493000000000001</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0665</v>
+        <v>-0.0895</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1588</v>
+        <v>-0.7934</v>
       </c>
       <c r="U5" t="n">
-        <v>1.2253</v>
+        <v>0.7039</v>
       </c>
       <c r="V5" t="n">
         <v>-2.1698</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.8979</v>
+        <v>-2.819</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8114</v>
+        <v>-2.9971</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.08649999999999999</v>
+        <v>0.1781</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.367</v>
+        <v>-2.1984</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9586</v>
+        <v>-0.0485</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4084</v>
+        <v>-2.1499</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9796</v>
+        <v>-1.2865</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6821</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2976</v>
+        <v>-0.6872</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3874</v>
+        <v>-0.9119</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2766</v>
+        <v>0.5508</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1108</v>
+        <v>-1.4627</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.9308</v>
+        <v>0.3862</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>1.3515</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4579</v>
+        <v>-1.0068</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5511</v>
+        <v>-0.7453</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.09320000000000001</v>
+        <v>-0.2615</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9421</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.3573</v>
+        <v>-3.2565</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.0557</v>
+        <v>-4.104</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6984</v>
+        <v>0.8474</v>
       </c>
       <c r="G7" t="n">
         <v>-3.2829</v>
@@ -1000,13 +1000,13 @@
         <v>1.5446</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2594</v>
+        <v>-0.1587</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4142</v>
+        <v>-0.4624</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1547</v>
+        <v>0.3037</v>
       </c>
       <c r="V7" t="n">
         <v>0.5712</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.6714</v>
+        <v>-3.3695</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.5764</v>
+        <v>-3.0595</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0951</v>
+        <v>-0.3099</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.1984</v>
+        <v>-2.367</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0485</v>
+        <v>-0.9586</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1499</v>
+        <v>-1.4084</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.2865</v>
+        <v>-1.9796</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5993000000000001</v>
+        <v>-0.6821</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6872</v>
+        <v>-1.2976</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9119</v>
+        <v>-0.3874</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5508</v>
+        <v>-0.2766</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.4627</v>
+        <v>-0.1108</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3862</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8592</v>
+        <v>-0.0137</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.3245</v>
+        <v>0.303</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5347</v>
+        <v>-0.3167</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.9421</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. DIOP</t>
+          <t>G. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.135</v>
+        <v>-5.3386</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4044</v>
+        <v>-5.3208</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.7307</v>
+        <v>-0.0178</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.6464</v>
+        <v>-2.4121</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5653</v>
+        <v>-2.4821</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2117</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0524</v>
+        <v>-1.4934</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6348</v>
+        <v>-2.7571</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6872</v>
+        <v>1.2637</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.594</v>
+        <v>-0.9187</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.06950000000000001</v>
+        <v>0.275</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5245</v>
+        <v>-1.1937</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3515</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>-3.8616</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5792</v>
+        <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5459000000000001</v>
+        <v>-0.5516</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5788</v>
+        <v>-0.5797</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0328</v>
+        <v>0.0281</v>
       </c>
       <c r="V9" t="n">
-        <v>-3.6831</v>
+        <v>0.3282</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.6138</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.6831</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. GUERRA LOZANO</t>
+          <t>P. DIOP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.122</v>
+        <v>-5.4121</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.9552</v>
+        <v>-1.756</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1668</v>
+        <v>-3.6562</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4121</v>
+        <v>-0.6464</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.4821</v>
+        <v>0.5653</v>
       </c>
       <c r="I10" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.2117</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4934</v>
+        <v>-0.0524</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.7571</v>
+        <v>0.6348</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2637</v>
+        <v>-0.6872</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9187</v>
+        <v>-0.594</v>
       </c>
       <c r="N10" t="n">
-        <v>0.275</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1937</v>
+        <v>-0.5245</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.7031</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8616</v>
+        <v>-1.9308</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1585</v>
+        <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3351</v>
+        <v>0.2689</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2141</v>
+        <v>0.2272</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1209</v>
+        <v>0.0417</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3282</v>
+        <v>-3.6831</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6138</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2856</v>
+        <v>-3.6831</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-22.0973</v>
+        <v>-20.9937</v>
       </c>
       <c r="E11" t="n">
-        <v>-21.1452</v>
+        <v>-20.0414</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9524000000000001</v>
+        <v>-0.9522000000000004</v>
       </c>
       <c r="G11" t="n">
         <v>-13.9309</v>
@@ -1285,13 +1285,13 @@
         <v>-12.2077</v>
       </c>
       <c r="J11" t="n">
-        <v>-9.403599999999999</v>
+        <v>-9.403600000000001</v>
       </c>
       <c r="K11" t="n">
         <v>-1.7178</v>
       </c>
       <c r="L11" t="n">
-        <v>-7.6859</v>
+        <v>-7.685899999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-4.527299999999999</v>
@@ -1303,7 +1303,7 @@
         <v>-4.5217</v>
       </c>
       <c r="P11" t="n">
-        <v>-3.8617</v>
+        <v>-3.861700000000001</v>
       </c>
       <c r="Q11" t="n">
         <v>-13.5156</v>
@@ -1312,28 +1312,28 @@
         <v>9.653700000000001</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.4482</v>
+        <v>-2.3442</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.2793</v>
+        <v>-3.1757</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8311999999999999</v>
+        <v>0.8313</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.8568999999999998</v>
+        <v>-0.8569</v>
       </c>
       <c r="W11" t="n">
         <v>6.053100000000001</v>
       </c>
       <c r="X11" t="n">
-        <v>-6.909999999999999</v>
+        <v>-6.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. MURRAY</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.2706</v>
+        <v>5.7111</v>
       </c>
       <c r="E12" t="n">
-        <v>0.4763</v>
+        <v>3.5424</v>
       </c>
       <c r="F12" t="n">
-        <v>4.7943</v>
+        <v>2.1686</v>
       </c>
       <c r="G12" t="n">
-        <v>1.8914</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3851</v>
+        <v>0.1033</v>
       </c>
       <c r="I12" t="n">
-        <v>2.2765</v>
+        <v>-0.1966</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0795</v>
+        <v>-0.7957</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.6598000000000001</v>
+        <v>-0.034</v>
       </c>
       <c r="L12" t="n">
-        <v>0.7393</v>
+        <v>-0.7617</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8119</v>
+        <v>0.7024</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2747</v>
+        <v>0.1373</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5372</v>
+        <v>0.5651</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7031</v>
+        <v>1.3515</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5916</v>
+        <v>-0.1723</v>
       </c>
       <c r="T12" t="n">
-        <v>1.1852</v>
+        <v>-0.5726</v>
       </c>
       <c r="U12" t="n">
-        <v>2.4065</v>
+        <v>0.4003</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9847</v>
+        <v>4.6251</v>
       </c>
       <c r="W12" t="n">
-        <v>1.1424</v>
+        <v>4.9108</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1271</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>A. VERA PICAZO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.227</v>
+        <v>5.0805</v>
       </c>
       <c r="E13" t="n">
-        <v>3.2322</v>
+        <v>2.9648</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9948</v>
+        <v>2.1157</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.09329999999999999</v>
+        <v>7.3912</v>
       </c>
       <c r="H13" t="n">
-        <v>0.1033</v>
+        <v>1.9994</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.1966</v>
+        <v>5.3918</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7957</v>
+        <v>5.6616</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.034</v>
+        <v>2.0692</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7617</v>
+        <v>3.5924</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7024</v>
+        <v>1.7296</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1373</v>
+        <v>-0.0698</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5651</v>
+        <v>1.7994</v>
       </c>
       <c r="P13" t="n">
-        <v>1.3515</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q13" t="n">
+        <v>-2.8962</v>
+      </c>
+      <c r="R13" t="n">
+        <v>2.3169</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.1994</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.5245</v>
+      </c>
+      <c r="V13" t="n">
+        <v>-2.4554</v>
+      </c>
+      <c r="W13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="n">
-        <v>1.3515</v>
-      </c>
-      <c r="S13" t="n">
-        <v>-0.6564</v>
-      </c>
-      <c r="T13" t="n">
-        <v>-0.8829</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0.2265</v>
-      </c>
-      <c r="V13" t="n">
-        <v>4.6251</v>
-      </c>
-      <c r="W13" t="n">
-        <v>4.9108</v>
-      </c>
       <c r="X13" t="n">
-        <v>-0.2856</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. VERA PICAZO</t>
+          <t>C. MURRAY</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.4115</v>
+        <v>3.4444</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0683</v>
+        <v>-0.5579</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3433</v>
+        <v>4.0023</v>
       </c>
       <c r="G14" t="n">
-        <v>7.3912</v>
+        <v>1.8914</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9994</v>
+        <v>-0.3851</v>
       </c>
       <c r="I14" t="n">
-        <v>5.3918</v>
+        <v>2.2765</v>
       </c>
       <c r="J14" t="n">
-        <v>5.6616</v>
+        <v>0.0795</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0692</v>
+        <v>-0.6598000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>3.5924</v>
+        <v>0.7393</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7296</v>
+        <v>1.8119</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0698</v>
+        <v>0.2747</v>
       </c>
       <c r="O14" t="n">
-        <v>1.7994</v>
+        <v>1.5372</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.5792</v>
+        <v>0.7723</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R14" t="n">
-        <v>2.3169</v>
+        <v>2.7031</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0549</v>
+        <v>1.7654</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3028</v>
+        <v>0.1509</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2479</v>
+        <v>1.6145</v>
       </c>
       <c r="V14" t="n">
-        <v>-2.4554</v>
+        <v>-0.9847</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.1424</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4554</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. MIJE BENITEZ</t>
+          <t>I. CONDES LOPEZ-CEPERO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4371</v>
+        <v>3.017</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.156</v>
+        <v>-0.4508</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5931</v>
+        <v>3.4678</v>
       </c>
       <c r="G15" t="n">
-        <v>1.4541</v>
+        <v>1.9081</v>
       </c>
       <c r="H15" t="n">
-        <v>0.62</v>
+        <v>-0.8204</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8341</v>
+        <v>2.7286</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3313</v>
+        <v>0.7164</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2069</v>
+        <v>-1.4403</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1244</v>
+        <v>2.1567</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1228</v>
+        <v>1.1917</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4131</v>
+        <v>0.6198</v>
       </c>
       <c r="O15" t="n">
-        <v>0.7098</v>
+        <v>0.5719</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.1239</v>
+        <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1101</v>
+        <v>0.2207</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1925</v>
+        <v>-0.5108</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0824</v>
+        <v>0.7315</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2856</v>
+        <v>-0.6565</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2856</v>
+        <v>-0.6565</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. CONDES LOPEZ-CEPERO</t>
+          <t>M. MIJE BENITEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3331</v>
+        <v>2.2717</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0713</v>
+        <v>-0.5697</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4044</v>
+        <v>2.8414</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9081</v>
+        <v>1.4541</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.8204</v>
+        <v>0.62</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7286</v>
+        <v>0.8341</v>
       </c>
       <c r="J16" t="n">
-        <v>0.7164</v>
+        <v>0.3313</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.4403</v>
+        <v>0.2069</v>
       </c>
       <c r="L16" t="n">
-        <v>2.1567</v>
+        <v>0.1244</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1917</v>
+        <v>1.1228</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6198</v>
+        <v>0.4131</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5719</v>
+        <v>0.7098</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5446</v>
+        <v>1.1585</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5446</v>
+        <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4632</v>
+        <v>-0.0552</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1313</v>
+        <v>-0.2212</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6681</v>
+        <v>0.166</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6565</v>
+        <v>-0.2856</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6565</v>
+        <v>0.2856</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6434</v>
+        <v>2.0793</v>
       </c>
       <c r="E17" t="n">
         <v>-0.7887999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4323</v>
+        <v>2.8681</v>
       </c>
       <c r="G17" t="n">
         <v>0.7964</v>
@@ -1780,13 +1780,13 @@
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1985</v>
+        <v>0.6344</v>
       </c>
       <c r="T17" t="n">
         <v>0.0825</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1161</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>1.2277</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4991</v>
+        <v>1.1377</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1722</v>
+        <v>-0.5859</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6713</v>
+        <v>1.7236</v>
       </c>
       <c r="G18" t="n">
         <v>0.5171</v>
@@ -1858,13 +1858,13 @@
         <v>0.3862</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5612</v>
+        <v>1.1998</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8270999999999999</v>
+        <v>0.4135</v>
       </c>
       <c r="U18" t="n">
-        <v>0.734</v>
+        <v>0.7863</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7244</v>
+        <v>0.7346</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.6362</v>
+        <v>-2.602</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9117</v>
+        <v>3.3365</v>
       </c>
       <c r="G19" t="n">
         <v>0.0659</v>
@@ -1936,13 +1936,13 @@
         <v>1.7377</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9488</v>
+        <v>0.5102</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.4072</v>
+        <v>-0.373</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4584</v>
+        <v>0.8832</v>
       </c>
       <c r="V19" t="n">
         <v>-0.6138</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>22.0974</v>
+        <v>23.4763</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9523000000000001</v>
+        <v>0.9520999999999997</v>
       </c>
       <c r="F20" t="n">
-        <v>21.1452</v>
+        <v>22.524</v>
       </c>
       <c r="G20" t="n">
         <v>13.9309</v>
@@ -1987,22 +1987,22 @@
         <v>12.2077</v>
       </c>
       <c r="J20" t="n">
-        <v>4.5273</v>
+        <v>4.527299999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.005400000000000071</v>
+        <v>0.005400000000000293</v>
       </c>
       <c r="L20" t="n">
         <v>4.5219</v>
       </c>
       <c r="M20" t="n">
-        <v>9.403499999999999</v>
+        <v>9.403500000000001</v>
       </c>
       <c r="N20" t="n">
         <v>1.7179</v>
       </c>
       <c r="O20" t="n">
-        <v>7.6859</v>
+        <v>7.685899999999999</v>
       </c>
       <c r="P20" t="n">
         <v>3.8616</v>
@@ -2014,16 +2014,16 @@
         <v>13.5154</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4479</v>
+        <v>4.827</v>
       </c>
       <c r="T20" t="n">
         <v>-0.8312999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>4.279299999999999</v>
+        <v>5.6582</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8567999999999996</v>
+        <v>0.8567999999999997</v>
       </c>
       <c r="W20" t="n">
         <v>6.91</v>
